--- a/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UC PARA LA VIDA)(1-56).xlsx
+++ b/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UC PARA LA VIDA)(1-56).xlsx
@@ -124,10 +124,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -176,10 +176,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -496,7 +496,7 @@
         <v>46252.40697916667</v>
       </c>
       <c r="D2" t="str">
-        <v>ncrubio@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -522,7 +522,7 @@
         <v>46252.407002314816</v>
       </c>
       <c r="D3" t="str">
-        <v>lcristinabernal@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -551,7 +551,7 @@
         <v>46252.415810185186</v>
       </c>
       <c r="D4" t="str">
-        <v>nestorjgarcia@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -580,7 +580,7 @@
         <v>46252.41725694444</v>
       </c>
       <c r="D5" t="str">
-        <v>hcastrof@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -609,7 +609,7 @@
         <v>46252.424108796295</v>
       </c>
       <c r="D6" t="str">
-        <v>dfpachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -638,7 +638,7 @@
         <v>46252.42422453704</v>
       </c>
       <c r="D7" t="str">
-        <v>sfvergara@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>46252.42444444444</v>
       </c>
       <c r="D8" t="str">
-        <v>smurciac@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -699,7 +699,7 @@
         <v>46252.42570601852</v>
       </c>
       <c r="D9" t="str">
-        <v>cbosa@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -731,7 +731,7 @@
         <v>46252.431076388886</v>
       </c>
       <c r="D10" t="str">
-        <v>rmunevar@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -763,7 +763,7 @@
         <v>46252.43140046296</v>
       </c>
       <c r="D11" t="str">
-        <v>clorenarodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -795,7 +795,7 @@
         <v>46252.43824074074</v>
       </c>
       <c r="D12" t="str">
-        <v>erpena@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -827,7 +827,7 @@
         <v>46252.64623842593</v>
       </c>
       <c r="D13" t="str">
-        <v>lvchiquiza@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>46252.64641203704</v>
       </c>
       <c r="D14" t="str">
-        <v>nalavardo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -885,7 +885,7 @@
         <v>46252.64760416667</v>
       </c>
       <c r="D15" t="str">
-        <v>jalejandrasarmiento@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -917,7 +917,7 @@
         <v>46252.64818287037</v>
       </c>
       <c r="D16" t="str">
-        <v>dalwjandrochaves@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v>46252.649664351855</v>
       </c>
       <c r="D17" t="str">
-        <v>yzsantana@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -978,7 +978,7 @@
         <v>46252.64979166666</v>
       </c>
       <c r="D18" t="str">
-        <v>hcarolinasierra@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1010,7 +1010,7 @@
         <v>46252.64991898148</v>
       </c>
       <c r="D19" t="str">
-        <v>vjcastro@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1042,7 +1042,7 @@
         <v>46252.65615740741</v>
       </c>
       <c r="D20" t="str">
-        <v>jprocha@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1071,7 +1071,7 @@
         <v>46252.65659722222</v>
       </c>
       <c r="D21" t="str">
-        <v>dandrespatino@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1103,7 +1103,7 @@
         <v>46252.656805555554</v>
       </c>
       <c r="D22" t="str">
-        <v>rjdelgado@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1135,7 +1135,7 @@
         <v>46252.65782407407</v>
       </c>
       <c r="D23" t="str">
-        <v>danielssuarez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>46252.65787037037</v>
       </c>
       <c r="D24" t="str">
-        <v>karolvrojas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1196,7 +1196,7 @@
         <v>46252.65820601852</v>
       </c>
       <c r="D25" t="str">
-        <v>ynmolina@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1228,7 +1228,7 @@
         <v>46252.65886574074</v>
       </c>
       <c r="D26" t="str">
-        <v>jbriseno@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1260,7 +1260,7 @@
         <v>46252.66243055555</v>
       </c>
       <c r="D27" t="str">
-        <v>hacorredor@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1289,7 +1289,7 @@
         <v>46252.662465277775</v>
       </c>
       <c r="D28" t="str">
-        <v>empachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1321,7 +1321,7 @@
         <v>46252.663506944446</v>
       </c>
       <c r="D29" t="str">
-        <v>jcarinagomez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1353,7 +1353,7 @@
         <v>46252.666180555556</v>
       </c>
       <c r="D30" t="str">
-        <v>eestibengarzon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1382,7 +1382,7 @@
         <v>46252.666493055556</v>
       </c>
       <c r="D31" t="str">
-        <v>ahvanegas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1414,7 +1414,7 @@
         <v>46252.66657407407</v>
       </c>
       <c r="D32" t="str">
-        <v>karendortiz@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1446,7 +1446,7 @@
         <v>46252.671273148146</v>
       </c>
       <c r="D33" t="str">
-        <v>kdrodriguezvelosa@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1475,7 +1475,7 @@
         <v>46252.67141203704</v>
       </c>
       <c r="D34" t="str">
-        <v>paulaaperez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1507,7 +1507,7 @@
         <v>46252.6721412037</v>
       </c>
       <c r="D35" t="str">
-        <v>krociomurcia@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1539,7 +1539,7 @@
         <v>46252.672314814816</v>
       </c>
       <c r="D36" t="str">
-        <v>kxvillamil@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1571,7 +1571,7 @@
         <v>46252.67255787037</v>
       </c>
       <c r="D37" t="str">
-        <v>jefersonalejandroramirez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1600,7 +1600,7 @@
         <v>46252.672638888886</v>
       </c>
       <c r="D38" t="str">
-        <v>rguilombo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1629,7 +1629,7 @@
         <v>46252.67377314815</v>
       </c>
       <c r="D39" t="str">
-        <v>yandreyrincon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1658,7 +1658,7 @@
         <v>46252.68006944445</v>
       </c>
       <c r="D40" t="str">
-        <v>nmhuertas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1687,7 +1687,7 @@
         <v>46252.68010416667</v>
       </c>
       <c r="D41" t="str">
-        <v>jalayon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1716,7 +1716,7 @@
         <v>46252.68015046296</v>
       </c>
       <c r="D42" t="str">
-        <v>ndalarcon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1745,7 +1745,7 @@
         <v>46252.681597222225</v>
       </c>
       <c r="D43" t="str">
-        <v>angiecrojas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1774,7 +1774,7 @@
         <v>46252.681608796294</v>
       </c>
       <c r="D44" t="str">
-        <v>yessicatrodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1803,7 +1803,7 @@
         <v>46252.68172453704</v>
       </c>
       <c r="D45" t="str">
-        <v>lncajamarca@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1832,7 +1832,7 @@
         <v>46252.682488425926</v>
       </c>
       <c r="D46" t="str">
-        <v>nleonr@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1861,7 +1861,7 @@
         <v>46252.811377314814</v>
       </c>
       <c r="D47" t="str">
-        <v>mangelpoveda@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -1896,7 +1896,7 @@
         <v>46252.81859953704</v>
       </c>
       <c r="D48" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I48" t="str">
         <v>Graduados</v>
@@ -1922,7 +1922,7 @@
         <v>46252.818657407406</v>
       </c>
       <c r="D49" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I49" t="str">
         <v>Graduados</v>
@@ -1954,7 +1954,7 @@
         <v>46252.81929398148</v>
       </c>
       <c r="D50" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I50" t="str">
         <v>Graduados</v>
@@ -1986,7 +1986,7 @@
         <v>46252.82019675926</v>
       </c>
       <c r="D51" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I51" t="str">
         <v>Graduados</v>
@@ -2018,7 +2018,7 @@
         <v>46252.821539351855</v>
       </c>
       <c r="D52" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I52" t="str">
         <v>Graduados</v>
@@ -2050,7 +2050,7 @@
         <v>46252.83293981481</v>
       </c>
       <c r="D53" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I53" t="str">
         <v>Creadores de Oportunidades (estudiantes)</v>
@@ -2082,7 +2082,7 @@
         <v>46252.832962962966</v>
       </c>
       <c r="D54" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I54" t="str">
         <v>Graduados</v>
@@ -2114,7 +2114,7 @@
         <v>46252.83662037037</v>
       </c>
       <c r="D55" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I55" t="str">
         <v>Graduados</v>
@@ -2143,7 +2143,7 @@
         <v>46252.83710648148</v>
       </c>
       <c r="D56" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I56" t="str">
         <v>Graduados</v>
@@ -2172,7 +2172,7 @@
         <v>46252.83752314815</v>
       </c>
       <c r="D57" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I57" t="str">
         <v>Graduados</v>
